--- a/samples/2026_진로탐색_사전사후.xlsx
+++ b/samples/2026_진로탐색_사전사후.xlsx
@@ -9389,7 +9389,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:M7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -9422,6 +9422,15 @@
       <c r="J1" t="str">
         <v>단위</v>
       </c>
+      <c r="K1" t="str">
+        <v>근거ID</v>
+      </c>
+      <c r="L1" t="str">
+        <v>근거 적용 사유</v>
+      </c>
+      <c r="M1" t="str">
+        <v>원문 검토</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -9454,6 +9463,15 @@
       <c r="J2" t="str">
         <v>회</v>
       </c>
+      <c r="K2" t="str">
+        <v>oecd-results-framework</v>
+      </c>
+      <c r="L2" t="str">
+        <v>활동 산출과 참여자 성과를 구분해 지표의 성과단계를 해석하는 데 적용</v>
+      </c>
+      <c r="M2" t="str">
+        <v>예</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -9486,6 +9504,15 @@
       <c r="J3" t="str">
         <v>명</v>
       </c>
+      <c r="K3" t="str">
+        <v>oecd-results-framework</v>
+      </c>
+      <c r="L3" t="str">
+        <v>활동 산출과 참여자 성과를 구분해 지표의 성과단계를 해석하는 데 적용</v>
+      </c>
+      <c r="M3" t="str">
+        <v>예</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -9518,6 +9545,15 @@
       <c r="J4" t="str">
         <v>점</v>
       </c>
+      <c r="K4" t="str">
+        <v>kywa-measurement-tools</v>
+      </c>
+      <c r="L4" t="str">
+        <v>동일 문항과 척도로 측정한 사전·사후 결과의 비교 가능성을 확인하는 데 적용</v>
+      </c>
+      <c r="M4" t="str">
+        <v>예</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -9550,6 +9586,15 @@
       <c r="J5" t="str">
         <v>점</v>
       </c>
+      <c r="K5" t="str">
+        <v>kywa-measurement-tools</v>
+      </c>
+      <c r="L5" t="str">
+        <v>동일 문항과 척도로 측정한 사전·사후 결과의 비교 가능성을 확인하는 데 적용</v>
+      </c>
+      <c r="M5" t="str">
+        <v>예</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -9582,6 +9627,15 @@
       <c r="J6" t="str">
         <v>%</v>
       </c>
+      <c r="K6" t="str">
+        <v>kywa-measurement-tools</v>
+      </c>
+      <c r="L6" t="str">
+        <v>동일 문항과 척도로 측정한 사전·사후 결과의 비교 가능성을 확인하는 데 적용</v>
+      </c>
+      <c r="M6" t="str">
+        <v>예</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -9614,10 +9668,19 @@
       <c r="J7" t="str">
         <v>점</v>
       </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/samples/2026_진로탐색_사전사후.xlsx
+++ b/samples/2026_진로탐색_사전사후.xlsx
@@ -9199,7 +9199,7 @@
         <v>참여대상</v>
       </c>
       <c r="C4" t="str">
-        <v>부천시 중·고등학생 100명</v>
+        <v>지역 중·고등학생 100명</v>
       </c>
       <c r="D4" t="str">
         <v/>
